--- a/Data/7052019-09062024/Split_Data/with_account/Scraped_Results/Vooruit_official.xlsx
+++ b/Data/7052019-09062024/Split_Data/with_account/Scraped_Results/Vooruit_official.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>hearts_count</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>transcription</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,10 +486,8 @@
           <t>hannelore.goeman</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7378209688141221153</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7.378209688141221e+18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -515,6 +518,11 @@
       <c r="I2" t="n">
         <v>125</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Wij geloven in de kracht van onze stad de kracht eh van onze jongeren dus elk kind een eerlijke kans om de beste versie te worden van zichzelf en wat uw ouders ook verdienen welke taal zou ik spreken dat is onze droom daar het best sterk onderwijs voor nodig genoeg goede betaalbare kinderopvang daar kan Vlaanderen echt het verschil maken maar heeft deze Vlaamse regering gevallen dus vooruit gaat bijvoorbeeld voor onderwijs eh en kinderen opvang want alleen als onze kinderen vooruitgang gaan wij ook gaan stappen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,10 +530,8 @@
           <t>hannelore.goeman</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7377700878205177121</t>
-        </is>
+      <c r="B3" t="n">
+        <v>7.377700878205177e+18</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -556,6 +562,11 @@
       <c r="I3" t="n">
         <v>55</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>We staan hier vandaag in sint-gillis eh met Willem Stevens onze schepen voor de jeugd en stadsvernieuwing op een prachtig nieuw initiatieven van de gemeente maar daar gaat weer op alles over vertellen We staan hier in het hartje van de Zuidwijk eh op voormalige ecam zitten en hier hebben we dankzij het werk contract een eh jeugdploeg gecreëerd Dat wil zeggen dat eh jongeren hier eh terecht kunnen met dat uw vragen u ziet ook een groot jeugdhuis en we hebben hier een scholen Dat is een studiebegeleiding project maar wat ook belangrijk is We staan in een wijk die heel dicht te bevolkt Is The Young is en waar dus heel weinig ruimte is voor kinderen en jongeren Maar dankzij dit project hebben we meer ruimte gecreëerd terug voor kinderen en jongen Je ziet het waar vooruit bestuurt gaat het vooruit met onze jongeren voordat we investeren in onze jongeren zodat ze ook na de schooluren kan ze krijgen om zich te ontwikkelen om bij te leren dus kies ook 9 juni voor onze jeugd kies voor vooruit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,10 +574,8 @@
           <t>hannelore.goeman</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7377404227234090273</t>
-        </is>
+      <c r="B4" t="n">
+        <v>7.37740422723409e+18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -592,11 +601,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11558</v>
+        <v>11560</v>
       </c>
       <c r="I4" t="n">
         <v>113</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>personne répond ici qu'est-ce que tu fais ici j'ai v'la je pensais que tu étais heureux parce que le Vlas Belan c'est totalement la même chose que le Front national que le parti de Zemmour que le rassemblement national c'est la même merde c'est pour cela qu'il faut voter pour vos rats puisque voja tu es le seul parti qui va contrer le</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,10 +618,8 @@
           <t>hannelore.goeman</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7376942600353352993</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7.376942600353353e+18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -633,11 +645,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6396</v>
+        <v>6397</v>
       </c>
       <c r="I5" t="n">
         <v>87</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>met zijn werk kost geld gemiddelde €12 principes en niet alle meisjes hebben die centen bij dat de helft van de meisjes die in armoede leven geven aan dat ze soms niet genoeg geld hebben om maandverband of tampons te kopen en dan lijkt natuurlijk tot schaamte tot angst en ook soms tot spijbelen gebracht en daarom heeft de stad Brussel beslist om in alle secundaire scholen menstruatieproducten gratis aan te bieden op die manier Nemen we een zorg weg en kan de Focus op het leren blijven een Prachtig initiatief maar het mag toch niet afhangen van de gemeente waar dat gewoon omdat je toegang hebt Tot menstruatieproducten en daarom blijten wij met vooruit om in alle scholen in Vlaanderen en Brussel gratis menstruatieproducten te voorzien Het is volgens ons de plicht van de Vlaamse gemeenschap omdat te doen en er wordt zorgen dat je zorgenloos kan leren vooruit strijd versterk en betaalbaar onderwijs voor elk kind hebben we jullie steun voor nodig elke stem telt het is voorraad of het is achteruit Kies maar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -645,10 +662,8 @@
           <t>hannelore.goeman</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7376534705312681249</t>
-        </is>
+      <c r="B6" t="n">
+        <v>7.376534705312681e+18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -679,42 +694,1150 @@
       <c r="I6" t="n">
         <v>67</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Wat een keer horen is eigenlijk gewoon zeggen witte scholen en zwarte scholen apartheid in het onderwijs allez dat is Classic eh Vlaams belang ehm Allez meneer loopt te stellen die morgen wil dat er Brusselaar zijn die ons kunnen helpen bij de politie of eh een ziekenhuis in het Nederlands dan moeten we onze scholen openhouden voor alle brusselaars in Nederland willen leggen of zo in Vlaanderen of in Brussel wonen We moeten er voor een zorgen dat leerkrachten niet afhaken en dat gaat inderdaad over het versterken van de lerarenopleiding maar dat gaat ook eerst en vooral over het aanpakken van werkdruk leerkrachten zijn vandaag aan het verzuipen dus nog even voor onderwijsassistente in de klas Ge moet The Planes aanpakken en dan brusselaars voor Brusselse klasse bijvoorbeeld Ja ik denk dat dat absoluut een prioriteit moet zijn dus laten we ons inzetten open voorbeeld scouting en trainingsprogramma's voor de scholieren in de in het middelbaar in het Nederlands toevallig onderwijs Laat alstublieft de hoofdrol in het onderwijs allez</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7.376384712916487e+18</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376384712916487456</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1717448409</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-06-03 14:00:09</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Comme Bruxellois.e, vous pouvez contrer la montée de l’extrême droite en votant pour Vooruit ce 9 juin. En votant pour Vooruit au Parlement bruxellois, vous pourrez aussi le faire pour le Parlement flamand. À gauche comme au centre, nous sommes le seul parti de Flandre assez important pour tenir l’extrême droite hors du gouvernement. C’est progresser avec Vooruit. Ou régresser. À vous de choisir. 👊 @Ans Persoons Official</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4515</v>
+      </c>
+      <c r="I7" t="n">
+        <v>47</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>la Flandre se dirige vers un horizon sombre le courant le risque de voir participer l'extrême droite au gouvernement et c'est un danger pour notre enseignement pour le secteur culturel et associatif pour toutes les minorités pour les droits de femmes et des personnes cuir pour l'avenir de notre pays à Bruxelles vous pouvez contrer l'extrême droite en votant pour vos rêves le Parti socialiste neurologue on votants vos rêves pour le Parlement bruxellois vous pouvez aussi voter pour le parti forest au Parlement flamand pour Flandres nous sommes le seul parti capable d'empêcher une majorité avec je prenne droite nous ne pouvons pas laisser des fascistes arriver au pouvoir en Flandre à Bruxelles et en Belgique nous devons faire bloc pour notre démocratie pour nos libertés pour nos droits ne soyez pas dupe foutez vos rêves</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7.376384124082212e+18</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376384124082212128</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1717448271</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024-06-03 13:57:51</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Filip Rogiers is ongetwijfeld één van de meest bijzondere zij-instromers in onze stad. Was 30 jaar lang journalist en werd begin september leerkracht Nederlands &amp; Engels in een Brussels atheneum. Daar ziet hij elke dag hoe sterk onderwijs een echte kansenmachine is voor zoveel jonge Brusselaars, maar ook hoe het schrijnende lerarentekort daar een grote bedreiging voor is. Nu engageert Filip zich ook voor de politiek. “Om mee de strijd te voeren voor goed onderwijs voor iedereen, niet enkel voor de elite. Én om mee blok te vormen tegen extreemrechts, want dat is voor iedereen een bedreiging. We hebben nood aan politici die opbouwen en niet afbreken.” Go go go, Filip! ❤️ ••• Filip Rogiers est sans aucun doute l’un des nouveaux venus à l’enseignement les plus à part dans notre ville. Il a été journaliste pour De Standaard pendant 30 ans et a commencé début septembre comme prof de néerlandais et d’anglais à une athénée à Bruxelles. Il y constate au quotidien à quel point un enseignement solide est un vrai moteur d’opportunités pour tellement de jeunes de Bruxelles, mais aussi à quel point la pénurie criante d’enseignant menace le système. Filip s’engage aujourd’hui également en politique. “Pour aider dans le combat pour un enseignement de qualité pour tous, pas seulement pour l’élite. Et pour contribuer à former un bloc contre l’extrême droite, parce qu’elle est un danger pour tout le monde. Nous avons besoin de responsables politiques qui construisent, pas qui démolissent.” Go go go, Filip ! ❤</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3169</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ik ben Filip Ik was jarenlang journalist sinds vorig jaar sta ik voor de klas en een Brusselse school en ik zie daar ongelooflijk mooie dingen Ik zie daar mensen die het vuur uit de sloffen lopen om Brusselse ketjes goeie toekomst te geven we los van een afkomst los van het inkomen of diploma van een auto maar ik zie helaas ook zorgwekkend te dingen en ik zie scholen die dicht moeten gaan wij gebruiken een leerkrachten ik kan leerkracht die Flexi Jobs moeten erbij pakken hebben op dit moment een minister die eigenlijk niet geeft om Brussel en soms vraag ik me af of er eigenlijk wel geeft om jongeren en daarom steun ik van Lauren Goeman en vooruit Brussels we hebben mensen nodig die voor een goed onderwijs zich kunnen inzetten u geen Elite onderwijs voor enkele maar goed onderwijs voor iedereen maar er is nog een reden waarom ik jou steunen Lauren dat is de strijd tegen extreem rechts het is geen vijf voor twaalf Het is 5 maal 12 en we moeten vooruit mensen die achteruit en daarom hebben we politici nodig zoals aan de horen die opbouwen en die afbreken daarom Hallo hoe mijn voorruit Brussels en mezelf natuurlijk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.376383519464885e+18</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376383519464885537</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1717448130</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024-06-03 13:55:30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brussel is geen eiland. Als Vlaams Belang aan de macht komt in Vlaanderen, zullen we daar in Brussel dubbel en dik de prijs voor betalen. Help ons om het Vlaams Belang te stoppen. Stem Vooruit.brussels. Elke stem telt. ••• Bruxelles n’est pas une île. Si le Vlaams Belang arrive au pouvoir en Flandre, nous en paierons le prix fort à Bruxelles. Aidez-nous à contrer le Vlaams Belang. Votez Vooruit.brussels. Chaque voix compte.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>19556</v>
+      </c>
+      <c r="I9" t="n">
+        <v>374</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Peter van Grieken eh Brussel is weer van ons maar in ons op wie slaat dat eigenlijk gaat dat ook voor vrouwen die pas na 1:30 de kinderen hebben gekregen die ons gaat dat ook voor onze prachtige lgbt de qua gemeenschap die ons zijn dat ook mensen met een migratieachtergrond of zoals jij ze noemt allochtonen bendes laat u niks wijsmaken Vlaams belang geeft geen energir om Brussel extreem rechts vormt een bedreiging voor onze vrijheid en voor het diverse DNA van onze stad is geen eiland dat is Vlaams belang aan de macht komt zo daar in Brussel de prijs voor betalen vooruit is de enige partij die is lenzen zijn kan stoppen tot de favoriete stemmen in Brussels parlement kan je ook voor voor het stemmen in het Vlaams parlement en mee blok voor me tegen extreem rechts helpt ons langs te stoppen elke stem telt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.376382771968658e+18</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376382771968658721</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1717447957</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024-06-03 13:52:37</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>@Safouane Akremi is een crème van een gast. Weet als geen ander waarom we moeten blijven investeren in ons Nederlandstalig onderwijs in Brussel. Als trots product van een Nederlandstalige beroepsschool wil hij dat ook de komende generaties Brusselaars sterk onderwijs krijgen. Want dat is een echte kansenmachine om vooruit te geraken. “Daarom sta ik op de Vlaamse lijst van Vooruit.brussels. Om te vechten voor meer inspanningen vanuit Vlaanderen voor ons Nederlandstalig onderwijs: meer plaatsen, meer leerkrachten en betaalbare schoolfacturen.” Heel veel succes, Safouane! ❤️ ••• Safouane est un camerade que j’admire. Il sait mieux que quiconque pourquoi nous devons continuer à investir dans notre enseignement néerlandophone à Bruxelles. Fier d’être issu d’une école professionnelle néerlandophone, il veut que les futures générations de Bruxellois puissent aussi bénéficier d’un enseignement solide. Parce que c’est le véritable moteur pour créer des opportunités et avancer dans la vie. “C’est pourquoi je me présente sur la liste flamande de Vooruit.brussels. Pour appeler la Flandre à en faire davantage pour l’enseignement néerlandophone : pour plus de places, plus d’enseignants et des factures scolaires abordables.” Bonne chance, Safouane! ❤️</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1082</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ik ben Stef van het Gods producten Ik wil een Nederlandstalig eh beroepsonderwijs Ik ben ook gemeenteraadslid tegen Anderlecht en ik ben ook vakmans secretaris bij BVV gewone mensen en vooruit te helpen dat is een van mijn doel en mijn leven oftewel dat je met je handen kan werken of met je hoofdstel denken Daarom moet je een wissel een Stack onderwijs en zodat we iedereen vooruit kan als ze willen dat één wisselen een ster komt er gewerkt hebben dan moet Vlaanderen ook meer doen zorgen dat er meer plaatsen zijn voor onze kinderen z terwijl we ook meer geleerd karakter hebben in onze scholen zorgen dat er ook betaalbare factuur zijn daarom schrijf ik ook voor een 6 Komt erbij samen met de handen Lauren Voerman hier geen Brussel Het is voorraad of het is echter uit Kies maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7.376380206702939e+18</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376380206702939425</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1717447369</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024-06-03 13:42:49</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Zeynep Balci is de kleindochter van een Turkse mijnwerker die naar België kwam om zijn familie een beter leven te geven, om hun kansen te vergroten. Die strijd om iedereen een eerlijke kans te geven wil Zeynep ook voeren in het vlaams parlement. “Vlaanderen beslist over ons onderwijs en laat net dat de sleutel zijn voor échte kansengelijkheid. Ik wil vechten voor nog sterker onderwijs in onze stad, zodat onze jonge Brusselaars alle mogelijke kansen kunnen krijgen en grijpen”. Go go go, Zeynep! ❤️ ••• Zeynep Balci est la petite-fille d’un mineur turc qui est venu en Belgique pour donner à sa famille une vie meilleure, pour augmenter leurs chances. Ce combat pour donner à chacun une chance équitable, Zeynep souhaite également le mener au sein du Parlement flamand. “La Flandre décide de notre enseignement et c’est la clé d’une véritable égalité des chances pour tous. Je veux me battre pour un enseignement encore plus fort dans notre ville, afin que nos jeunes Bruxellois.es puissent obtenir et saisir toutes les opportunités possibles.” Allez, allez, allez, Zeynep ! ❤️</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>25650</v>
+      </c>
+      <c r="I11" t="n">
+        <v>403</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ik ben Zeynep en Ronald 20 jaar in Brussel Het was Mijn grootvader die naar België kwam om in de steenkoolmijn te werken een zware Job maar toegewijd om zijn familie alle kans te geven en daar Daar begint mijn verhaal mijn studies brachten mij naar Brussel een keuze waar ik nog steeds volledig achter staat al kunnen er veel dingen veel beter in deze stad Ik zie nog te veel mensen die zich dubbel zo hard moeten bewijzen en geen netwerk hebben om hem te helpen richting een goede Job of degelijk onderwijs Ik zie ook Talent veel Talent en ik wil dat elk Brussels kind de kansen grijpt maar daar ook de kansen voor krijgt en daar is onderwijs de sleutel voor en daarom schrijf ik samen met Hannelore voor sterker onderwijs Het is vooruit of het is achteruit Kies maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7.376376523487448e+18</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7376376523487448353</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1717446502</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024-06-03 13:28:22</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>We hebben de afgelopen weken met veel Brusselaars gepraat. En we hebben de boodschap begrepen: “Los het op.” Brussel staat op een kantelpunt. Het is tijd voor eerlijke lonen, volle brooddozen, een leerkracht voor de klas, betaalbare woningen, echte fietspaden, propere straten en veilige metrostations. Wij kunnen dat. ••• Nous avons discuté avec énormément de Bruxellois.ses ces dernières semaines. Et nous avons bien compris votre message : “Allons. Réglons les problèmes.” Bruxelles est à un tournant. Le temps est venu pour des salaires décents, des boîtes à tartines remplies pour nos enfants, un prof dans chaque classe d’école, des logements abordables, de vraies pistes cyclables, des rues propres et des stations de métro sûres. Nous pouvons y arriver ensemble. 🙌 @Ans Persoons Official</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3280</v>
+      </c>
+      <c r="I12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ik ben Ans en ik ben Hannelore Wij zijn de lijsttrekkers van vooruit Brussels en we hebben de voorbij weken met heel veel brusselaars reparatie en we hebben de boodschap begrepen politici stop met ruzie maken en los het op Brussel staat op een kantelpunt de uitdagingen zijn enorm we moeten Brussel proper veilig en betaalbaar maken we gaan het niet oplossen op tiktok of door mensen tegen elkaar op te zetten Laat extreme Brussel niet blokkeren keihard werken trekken en sleuren over partij geen Daarvoor kan je op ons rekenen los het op wij kunnen dat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7.367845322988539e+18</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7367845322988539168</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1715460176</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024-05-11 13:42:56</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1 op 10 kinderen in Vlaanderen en Brussel heeft vandaag niet de zekerheid om iets deftig te eten. Toch blijven minister Dalle en de Vlaamse regering deze schande wegrelativeren. Nee, het mag niet afhangen van de goodwill van een vzw of een gemeentebestuur of onze kinderen al dan niet een lege of ongezonde brooddoos hebben. De Vlaamse regering, bevoegd voor onderwijs en armoedebestrijding, moet ervoor zorgen dat elk kind kan leren. En dat is onmogelijk op een lege maag. @Vooruit</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3611</v>
+      </c>
+      <c r="I13" t="n">
+        <v>62</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>en stärke overheid die kan daar iets aan doen hè Het mag niet afhangen van de goodwill van de VZW u kan mij niet garanderen dat morgen elk kind in Vlaanderen de zekerheid heeft van een deftige maaltijd uh laat onze kinderen in de steek alweer een boom dat is echt een Legacy van deze Vlaamse regering en inderdaad hè armoede bestrijding is geen beleid dat alleen maar gaat overleden brooddozen maar ik denk niet dat ik daar van u iets te leren hebben te leren Heb met een partij die 1 miljard heeft bespaart op de kinderbijslag</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.365835545051729e+18</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7365835545051729184</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1714992241</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024-05-06 03:44:01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jij en niemand anders kiest straks hoe onze toekomst eruit ziet. Hoe de toekomst van onze kinderen zruit ziet. Hoe de toekomst van onze stad eruit ziet. Het is @Vooruit. Of het is achteruit. Kies maar.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1858</v>
+      </c>
+      <c r="I14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>een mooie toekomst voor je kind dat is wat elke ouder wil als ik in de klas van mijn zoontje kom dan zie ik zoveel potentieel allemaal kleine brusselaars elk met hun eigen dromen dan zie ik de politie mensen verplegers de ondernemers vanmorgen alleen wordt er vandaag massaal gemorst meer een Talent wordt er gespeeld met hun kansen en dus met hun toekomst en onze welvaart Ik weiger die stilstand aan achteruitgang dat is een keuze Maar ja wat is jij wil je nog minder leerkrachten voor de klas en kinderen die geen kansen krijgen om hoe Nederlands te leren of gaan we opnieuw zorgen voor sterk onderwijs en een plek voor elk kind wil je een Vlaamse regering die Brusselse krasjes en scholen onbetaalbaar maakt of gaan we eindelijk investeren in onze aller kleinste Wil je een extremistische regering die onze super diverse stad kapot maken of gaan we voor een Vrij veilig Brussel maar elk kind een eerlijke kans krijgt om vooruit te gaan jij en niemand anders kiest straks moet de toekomst er zal uitzien en die keuze is heel simpel het eens voor Oh wat is achteruit Kies maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7.365103946706243e+18</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7365103946706242848</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1714821901</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024-05-04 04:25:01</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wie de hartverscheurende verhalen uit #Godvergeten heeft gezien, beseft als geen ander dat slachtoffers van seksueel geweld absoluut niet altijd de erkenning en hulp hebben gekregen die ze nodig hebben. Waar ze recht op hebben. Dat is exact waarom de commissie seksueel misbruik in het Vlaams Parlement in het leven werd geroepen. Als voorzitter van die commissie ben ik dankbaar 101 concrete aanbevelingen te mogen voorstellen die moeten zorgen dat slachtoffers van vroeger, nu en morgen voortaan wel gezien, gehoord en geholpen worden oa. met een fonds voor geestelijke gezondheidszorg voor slachtoffers waartoe ook de Kerk een bijdrage zal moeten leveren. Én een resem oplossingen die zoveel mogelijk moeten voorkomen dat er nieuwe slachtoffers vallen.  Seksueel misbruik is een aanslag op je leven en zorgt voor littekens die je altijd blijft meedragen. Dat zal ik nooit vergeten uit al de getuigenissen die we hebben gehoord. We zijn het aan slachtoffers verschuldigd om voor hen te blijven opkomen en te zorgen dat onze kinderen, onze burgers, beter worden beschermd.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1937</v>
+      </c>
+      <c r="I15" t="n">
+        <v>23</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>aangegrepen door de vele verhalen komt de commissie met 101 aanbevelingen zo moet er opnieuw een moment van publieke excuses komen want sommige slachtoffers voelen zich nog steeds niet gehoord en daarom vind ik het belangrijk dat zowel de kerk maar wij ook als samenleving en dus wij als parlementsleden en vertegenwoordigers van die samenlevingen ook dit moment nog eens heel expliciet aangrijpen om te zeggen van kijk maar wij hebben nu wel gezien We hebben nu wel gehoord en Wij willen ons publiek excuseren voor het onmiddellijke Le vieze aangedaan maar er moet ook een expertisecentrum worden opgericht die onder meer zorgt voor een overzicht in het hulpaanbod en voor meer onderzoek want daar is nood aan hebben we echt heel erg En geslaagd zijn om binnen onze eigen bevoegdheden eh Vlaams en federaal en aantal heel concrete aanbevelingen te doen de commissie hoop dat de aanbevelingen realiteit worden ze zijn in elk geval door alle partijen goedgekeurd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7.364448174762626e+18</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7364448174762626336</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1714669213</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2024-05-02 10:00:13</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Anaïs ken ik als een vrouw die van aanpakken weet. Als leerkracht geschiedenis heeft ze voor veel van haar leerlingen het verschil gemaakt. Nu gebruikt ze die terreinkennis om hetzelfde te doen voor nog veel meer Brusselaars als schepen van onder meer Nederlandstalig Onderwijs in Stad Brussel. Ze weet daarom als geen ander hoe deze Vlaamse regering de Brusselse scholen compleet in de steek heeft gelaten: klassen die sluiten, lege brooddozen, dalende resultaten. Veel verder dan wat vingerwijzen is Minister Weyts niet geraakt. “Daarom sta ik op de Vlaamse lijst van Vooruit in Brussel. Om mee te strijden voor een Vlaanderen dat investeert in gratis schoolmaaltijden, betaalbaar onderwijs en sterke leerkrachten voor de klas.” Go go go, Anaïs! ❤️ ••• Anaïs est une femme qui sait comment faire avancer les choses. En tant que prof d’histoire, elle a fait la différence pour beaucoup de ses élèves. Aujourd’hui, elle utilise cette connaissance du terrain pour faire la même chose pour beaucoup d’autres Bruxellois.es en tant qu’échevine de l’Enseignement néerlandophone à la Ville de Bruxelles, entre autres choses. Elle sait donc mieux que quiconque à quel point le gouvernement flamand a laissé tomber les écoles bruxelloises : fermeture de classes, boîtes à tartines vides, baisse des résultats. Le ministre Weyts se contente de pointer du doigt. “C’est pourquoi je suis sur la liste flamande du Vooruit à Bruxelles. Pour aider à lutter pour une Flandre qui investit dans des repas scolaires gratuits, une éducation abordable et des enseignants forts devant la salle de classe.” Go go go, Anaïs! ❤️ @Vooruit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>5973</v>
+      </c>
+      <c r="I16" t="n">
+        <v>159</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ik ben een Anaïs en ik ben Schepen van Nederlandstalig onderwijs in de stad Brussel maar ik ben ook mama van een 10-jarig ketchup en ik heb zelf 12 jaar lang als leerkracht geschiedenis in Etterbeek voor de klas gestaan de Vlaamse regering die heeft leerkrachten directies ondersteunend personeel ouders maar vooral onze leerlingen structureel in de kou laten staan leeg brooddozen Dylan de pizza resultaat en het nieuwe van het Nederlands altijd de schuld van iemand anders en zeker niet de verantwoordelijkheid van Ministerie menu en dat moet anders daarom ga ik samen met Hannelore voor het beste onderwijs gratis schoolmaaltijden betaalbaar onderwijs en sterke leerkrachten voor de klas Het is voorraad of het is achteruit Kies maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.364397424242085e+18</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7364397424242085152</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1714657399</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024-05-02 06:43:19</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Terugblik op een zalige, zonnige, feestelijke, maar ook strijdbare 1 mei. Brussel staat op een kantelpunt. Vooruit wil de problemen aanpakken waar iedereen van wakker ligt: betaalbare woningen, sterk onderwijs en nette &amp; veilige buurten. Zo maken we de stad opnieuw van iedereen! Het is Vooruit. Of het is achteruit. Kies maar. 🌹 ••• Rétrospective sur un 1er mai super chouette, festif et ensoleillé, mais aussi combatif. Bruxelles est à un tournant. Vooruit veut s'attaquer aux problèmes de tous : logements abordables, enseignement, quartiers sûrs et propres. Nous rendrons ainsi la ville à tous.tes ! C'est progresser avec Vooruit, ou régresser. À vous de choisir.🌹</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1254</v>
+      </c>
+      <c r="I17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kus It's A Beautiful som mijn feestje nog geen domme giveaway It's A Beautiful you so much You Know It's so ieder geval heel goed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7.36373783734428e+18</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7363737837344279841</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1714503828</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2024-04-30 12:03:48</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>𝐁𝐫𝐮̈𝐤𝐬𝐞𝐥𝐝𝐞 𝐅𝐥𝐚𝐦𝐚𝐧 𝐨𝐤𝐮𝐥𝐥𝐚𝐫𝐢 𝐢𝐥𝐞 𝐢𝐥𝐠𝐢𝐥𝐢 𝐬𝐨𝐫𝐮𝐥𝐚𝐫? 👶🏽🏫 Brüksel’deki Flamanca kreşler ve okullar oldukça popüler olsa da, birçok Flamanca bilmeyen ebeveyn çeşitli zorluklarla karşılaşıyor ve endişe duyuyorlar: karmaşık kayıt prosedürleri, mevcut yer sayısı, yetersiz bakıcı ve öğretmenler, yüksek faturalar, kreş veya okulla iletişim sorunları... 👩🏼‍🏫 Brüksel’deki Flamanca eğitimini iyileştirmek Vooruit.brussels için bir öncelik ve sizin endişeleriniz bizi ilgilendiriyor! Flaman Kreşleri ve Flamanca eğitim konusunda yetkili olan Flaman Hükümeti’dir. Vooruit.brussels, tüm Brükselli ebeveynlerin dile getirdiği endişelerin Flaman Parlamentosu’nun çalışmalarında ele alınmasını talep ediyor. 🎤👂 Brüksel Bölgesi Flaman Parlamentosu Milletvekili Hannelore Goeman ve Vooruit.brussels adayı @Zeynep.Balcibxl, sizin için burada.  🤗 Bu Pazar 5 Mayıs öğleden sonra saat 14:00’de yapılacak söyleşiye herkesi bekliyoruz! Çocuklarınız da gelebilir, bakıcı sağlıyoruz (ücretsiz). Adres: CHP Belçika Birligi - Avenue Rogier 29 - Schaarbeek ••• 𝐐𝐮𝐞𝐬𝐭𝐢𝐨𝐧𝐬 𝐬𝐮𝐫 𝐥𝐞𝐬 𝐞́𝐜𝐨𝐥𝐞𝐬 𝐧𝐞́𝐞𝐫𝐥𝐚𝐧𝐝𝐨𝐩𝐡𝐨𝐧𝐞𝐬 𝐚̀ 𝐁𝐫𝐮𝐱𝐞𝐥𝐥𝐞𝐬? 🏫 Bienvenue ce dimanche 5 mai à 14h au CHP, avenue Rogier 29 à Schaerbeek. Avec Vooruit.brussels, nous y organisons un après-midi de débat sur l’enseignement néerlandophone à Bruxelles. 🎤👂Hannelore Goeman, Députée bruxelloise au Parlement Flamand est à votre écoute ainsi que Zeypnep Balci, candidate pour Vooruit.brussels. 👶🏼 Une garderie gratuite est prévue.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>3320</v>
+      </c>
+      <c r="I18" t="n">
+        <v>32</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>met Rabobank uitdagingen hè complexe inschrijvingsprocedure is moeilijk op een plaats te vinden leraren tekort Hogeschool facturen en soms ook gewoon niet evident om met de school te communiceren Hannelore Goeman</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7.36339179619964e+18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7363391796199640352</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1714423258</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024-04-29 13:40:58</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>On parle souvent des parents allophones au Parlement, mais trop rarement avec eux. Nous essayons de changer la donne avec nos après-midi de discussions sur les difficultés dans l'enseignement néerlandophones. Ce que j'en retiens surtout : les parents de Bruxelles partagent les mêmes préoccupations peu importe la langue parlée à la maison - les enfants qui passent des heures en fourche faute de prof et qui ne bénéficient pas du soutien dont ils ont besoin, absence d'offre extrascolaire suffisante... Merci @Saliha Raiss et Cem Aydogan pour cette après-midi passionnante. Prochains rendez-vous le 4 mai à Schaerbeek avec Zeynep Balci et le 12 mai à Anderlecht avec Safouane Akremi et Bieke Comer. Stay tuned ! ••• Er wordt in het parlement te veel gepraat over anderstalige ouders, maar veel te weinig mét hen. Daar proberen wij verandering in te brengen met onze gespreksnamiddagen over de uitdagingen in het Nederlandstalig onderwijs. Wat ik vooral onthoud: Brusselse ouders liggen vooral van dezelfde dingen wakker liggen, los van de taal die thuis gesproken wordt: kinderen die uren in de studie zitten bij gebrek aan leerkracht, leerlingen die niet de ondersteuning krijgen die ze nodig hebben, gebrek aan betaalbaar buitenschools aanbod, … Merci, Saliha Raiss en Cem Aydogan voor de bijzonder interessante namiddag. Volgende edities op 4 mei in Schaarbeek met Zeynep Balci  en op 12 mei in Anderlecht met Safouane Akremi en Bieke Comer. Stay tuned!</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1273</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pyrénées</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7.362199822767607e+18</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7362199822767607073</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1714145730</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024-04-26 08:35:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Waar @Vooruit bestuurt, gaat het vooruit met onze #kinderopvang. Ook in Anderlecht, met onze schepen Bieke Comer. Samen bezochten we het gemeentelijke kinderdagverblijf De Zonnebloem. Opnieuw zwaar onder de indruk van het engagement van de kinderbegeleidsters die dag in dag uit onze jongste Brusselaars mee opvoeden, in niet altijd even gemakkelijke werkomstandigheden.  Met Vooruit strijden we voor sterke en betaalbare kinderopvang. Meer plaatsen, minder kindjes per begeleider en 130 dagen gratis kinderopvang voor elk kind. Want een goede start van het leven, die begint in de crèche. ••• Là où Vooruit est aux manettes, nos crèches vont de l'avant. Aussi à Anderlecht, avec notre échevine Bieke Comer. Nous avons visité ensemble la crèche communale "De Zonnebloem". Une fois de plus, j'ai été profondément impressionnée par l'engagement des accompagnatrices qui contribuent à l'éducation des plus jeunes Bruxellois.es, jour après jour, dans des conditions de travail pas toujours faciles.  Avec Vooruit, nous nous battons pour des crèches fiables et abordables. Plus de places, moins d'enfants par accueillante et 130 jours gratuits pour chaque enfant. Parce qu'un bon départ dans la vie commence dès la crèche.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>816</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Hallo We zijn hier vandaag en kinderdagverblijf De Zonnebloem één van onze vier gemeentelijke kinderdagverblijven zijn nog een 5 aan het bouwen want we vinden het heel belangrijk om als gemeente veel te investeren en kinderdagverblijven ja want we weten dat hij die eerste 1000 dagen zijn zo ongelooflijk belangrijk Een goede start niet leven begint echt in de crèche Daarom is de kinderen opvang van vooruit een absolute prioriteit meer betaalbare plaatsen minder kindjes per begeleider betere arbeidsomstandigheden ehm daarom daar doen voor ehm dat is duidelijk denk ik hè Waarvoor het bestuurd gaat het vooruit met de kinderen opvang</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7.360651867870793e+18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7360651867870792992</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1713785323</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024-04-22 04:28:43</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Alors que nos écoles souffrent de la pénurie d’enseignants, de nombreuses jeunes femmes talentueuses ne sont pas autorisées à enseigner parce qu’elles portent un foulard. C’est un véritable gâchis de talents. Toute personne motivée qui souhaite et a les acquis pour enseigner mérite notre soutien. Ce n’est en effet pas ce qui est sur la tête qui compte, mais bien ce qui s’y trouve à l’intérieur. ••• Terwijl onze scholen kreunen onder het leerkrachtentekort, mogen veel getalenteerde jonge vrouwen geen les geven omdat... ze een hoofddoek dragen. Dat is zo’n verspilling van talent. Iedereen die de juiste motivatie heeft om de voor de klas te staan, verdient onze steun. Niet wat er op je hoofd staat telt, maar wat er in je hoofd zit. @Vooruit</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3649</v>
+      </c>
+      <c r="I21" t="n">
+        <v>39</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>je dois pas vous l'expliquer il y a une manque de prof énorme dans les écoles francophones comme néerlandophone et c'est un problème gigantesque pas de prof pas d'enseignement pour nos enfants c'est incompréhensible et inacceptable qu'au jour d'aujourd'hui des enfants se retrouvent dans une classe où il y a pas de prof alors que nous avons des personnes talentueux compétentes qui peuvent donner cours à ses élèves mais malheureusement on veut on veut refuser puisqu'elle porte un bout de tissu sur et c'est pour ça que vous dit maintenant oh non la chance aux femmes qui portent un voile de donner des cours de travailler dans notre enseignement parce qu'il y a sur la tête mais qui est dans la tête qui compte pour nous et en plus c'est une solution réelle pour la pénurie profs aujourd'hui</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7.359861997824953e+18</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7359861997824953632</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1713601417</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024-04-20 01:23:37</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Boek nu je huiskamerdebat met ons of andere kandidaten van Vooruit.brussels 👉 forms.office.com/e/w5vp8Gv3Bm</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1218</v>
+      </c>
+      <c r="I22" t="n">
+        <v>34</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>wil je graag weten hoe het in Brussel het onderwijs de kinderopvang De netheid op veiligheid wil verbeteren of hoe verzorgen dat jij er een betaalbare woning kan kopen of huren wij in onze kandidaten gaan erover graag een gesprek tijdens een huiskamer te laat inschrijven kan via onderstaande link</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7.359272839540788e+18</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7359272839540788512</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1713464238</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024-04-18 11:17:18</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Het is @Vooruit. Of het is achteruit. Kies maar.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>7910</v>
+      </c>
+      <c r="I23" t="n">
+        <v>168</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>de boodschap in het programma heeft heel duidelijk hè Wij moeten meer kinderen maken liefst eh voor ons 30e hè Hoe vroeger hoe beter zoals vroeger hè zoals de toen de vrouwen ook nog aan de hart zaten ehm maar ik heb een duidelijke boodschap voor jullie vrouwen zijn natuurlijk meer dan broed kippen die thuis gaan zitten wachten zodat de mannen hè de beslissingen kunnen gaan nemen voor ons in de jaren 50 zijn al lang voorbij gelukkig</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7.358570183281135e+18</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7358570183281134881</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1713300639</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024-04-16 13:50:39</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ook in Brussel is psychologische zorg dankzij Frank Vandenbroucke en @Vooruit een stuk goedkoper en toegankelijker geworden. Voor een sessie bij een psycholoog in de eerstelijnszorg betaal je nog maar 11 euro. Voor jongeren onder de 24 is het zelfs helemaal gratis.  Een systeem dat werkt, want al bijna 40.000 Brusselaars bezochten sinds september 2021 een psycholoog of orthopedagoog. Op nationaal niveau gaat het zelfs over 315.000 mensen. Maar het werk is nog niet af. We blijven vechten voor mentaal welzijn. ••• Aussi à Bruxelles, les soins psychologiques sont devenus moins chers et plus accessibles grâce à Frank Vandenbroucke et Vooruit. Une séance chez un psychologue de première ligne ne coûte plus que 11 euros. Pour les jeunes de moins de 24 ans, c'est même totalement gratuit.  Un système qui fonctionne, car près de 40 000 Bruxellois ont consulté un psychologue ou un orthopédagogue depuis septembre 2021. Au niveau national, ce chiffre s'élève même à 315 000 personnes. Mais le travail n'est pas encore terminé. Nous continuons à nous battre pour le bien-être mental.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3083</v>
+      </c>
+      <c r="I24" t="n">
+        <v>77</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Wie is een been breekt die gaat naar de spoed die zich slecht voelt in zijn vel moet even van zijn spreken naar de psycholoog kunnen dankzij Frank van den broecke en vooruit is dat nu ook echt zo want Franck voor de systeem en van betaalbare en toegankelijke psychologische hulp voor dan kan je voor €11 naar een 1e lijst psycholoog voor jongeren onder de 24 is het zelfs helemaal gratis en dan werkt intussen hem al meer dan 315000 Belgische gebruikt maakt van systeem in Brussel zijn er 36.000 €212500 jongeren mensen die nu wel geholpen worden zoals hier in het wijkgezondheidscentrum in Schaarbeek dus we hebben heel belangrijke stappen gezet maar het werk is niet af dus maar één partij voor wie mentaal wil zijn een echte prioriteit is en dat is vooruit dus weet waarvoor je kiest op negen juni</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7.356187435333701e+18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7356187435333700896</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1712745865</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024-04-10 03:44:25</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Meet Damienne. Ik heb de voorbije jaren heel veel fantastische leerkrachten ontmoet maar Damienne heeft een speciaal plaatsje in mijn hart. Ze staat dit jaar exact 20 jaar voor de klas in een Molenbeekse beroepsschool en ik heb zelf gezien hoe ze écht het verschil maakt voor onze jongeren, ook als het een gevecht bergop is. “Onderwijs is mijn grote passie, maar de uitdagingen worden steeds groter: taalachterstand , armoede en uiteraard, het lerarentekort. Daarom sta ik mee op de Vlaamse lijst van @vooruit.brussels. Om op te komen voor een sterk onderwijs met sterke leerkrachten. Voor een echte herwaardering van het beroepsonderwijs ook, zodat alle jongeren erop vooruitgaan. Of ze nu goed zijn met hun hoofd of hun handen.” Merci, Damienne ❤️ ••• Faites connaissance avec Damienne. J'ai rencontré énormément de profs fantastiques ces dernières années, mais Damienne a une place à part dans mon cœur. Elle enseigne depuis tout juste 20 ans dans une école professionnelle de Molenbeek et j'ai vu par moi-même comment elle peut faire réellement la différence pour nos jeunes, même quand les chances sont contre eux. "Cette année, cela fera 20 ans tout juste que j'enseigne dans une école professionnelle de Molenbeek. Enseigner est ma grande passion mais les difficultés s'accumulent : déficit linguistique, précarité et, bien entendu, pénurie d'enseignants." Je me présente donc à Bruxelles sur la liste flamande de Vooruit. Pour un enseignement fort et pour les enseignants. Pour une véritable revalorisation de l'enseignement professionnel aussi, pour que tous les jeunes puissent progresser. Qu'ils soient doués de leur tête ou de leurs mains." Un grand merci à toi, Damienne ❤️ @Vooruit</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1232</v>
+      </c>
+      <c r="I25" t="n">
+        <v>34</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ik ben Damien sinds 2004 precies 20 jaar sta ik in het beroepsonderwijs te Brussel en het is dagelijks Knokke want we kennen het leraren tekort ook armoede de taalachterstand en het wordt ringen tijd dat de praktijkonderwijs meer her waardeert wordt zodat knopen beroepen geen knelpunt hoeven te zijn en het is al Vlaanderen het Vlaams parlement dat verantwoordelijk en bevoegd is voor ons Nederlandstalig onderwijs te Brussel Daarom sta ik op de lijst voor het Vlaams voor vooruit en steun ik 100% Hannelore als lijsttrekker Het is vooruit of het is achteruit Kies maar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7.35448669646709e+18</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7354486696467090721</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1712349880</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024-04-05 13:44:40</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Alors que les vacances de Pâques dans l’enseignement néerlandophone sont déjà à moitié terminées, les vacances dans l’enseignement francophone n’ont pas encore commencé. Deux rythmes scolaires différents dans une même ville, c’est un chaos total. C’est pourquoi, avec @Vooruit, nous plaidons en faveur d’une harmonisation des rythmes scolaires dans les deux communautés. En tant que Bruxellois, nous ne vivons pas sur des îles néerlandophones et francophones, nous voulons surtout vivre ensemble. ••• Terwijl de paasvakantie in het Nederlandstalig onderwijs al halfweg is, moet die in het Frantalig onderwijs nog beginnen. Twee verschillende schoolvakantie-regelingen in één stad, dat is en blijft een totale chaos. Daarom pleiten we er met Vooruit voor om de vakantieregelingen in beide gemeenschappen opnieuw gelijk te schakelen. Als Brusselaars leven we niet op Nederlandstalige en Franstalige eilanden, we willen vooral samenleven. 📻 @AraBel FM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I26" t="n">
+        <v>28</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>les vacances scolaires avec un système différent dans les écoles néerlandophones et francophones créent une situation complètement kafkaïenne on sait bien que la bruxellois n'habite pas sur des îles et qui a beaucoup de familles bosawas qui ont des enfants dans les deux systèmes donc soit dans les icônes de Van soit aussi dans nos écoles francophones et pour s'organiser comme famille sur ces deux systèmes c'est complètement fou pour ça que aussi au niveau de Parlement flamand ou eh moi je suis membre du Parlement on va défendre maintenant l'idée que ça doit changer du côté</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7.353692310757985e+18</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7353692310757985569</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1712164920</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024-04-03 10:22:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Met trots stel ik jullie voor aan Jos. Jos heeft jarenlang de Vlaamse cultuuradministratie geleid, geniet nu van zijn welverdiend pensioen en staat als 6de opvolger op de Vlaamse lijst van Vooruit in Brussel. ❤️   "Als oud-cultuurambtenaar bij de Vlaamse Gemeenschap weet ik hoe belangrijk de investeringen van Vlaanderen in het Brusselse cultuurveld zijn. Vraag dat ook maar aan onze fantastische cultuurhuizen zoals de KVS, Bronks of de AB. Daarom sta ik mee op onze Brusselse lijst voor het Vlaams parlement.  Om op te komen voor een ambitieus Vlaams cultuurbeleid in Brussel en tégen extreemrechts. Want als die het straks voor het zeggen krijgen in Vlaanderen, maken ze meteen komaf met het kritische en open karakter dat ons culturele veld vandaag zo sterk maakt.“  U leest het: deze man is absoluut uw stem waard. ••• Je suis fière de vous présenter Jos. Jos a dirigé l'administration culturelle flamande pendant de longues années et profite aujourd'hui d'une retraite bien méritée. Il est le 6e candidat suppléant sur la liste bruxelloise de Vooruit pour le Parlement flamand. ❤ "Comme ancien responsable de la culture au sein de l’administration flamande, je sais à quel point les investissements faits par la Flandre dans le domaine culturel bruxellois sont importants. Nos institutions culturelles telles que le KVS, le Bronks ou l'AB en sont les parfaits témoins. C'est pourquoi je figure sur notre liste bruxelloise pour le Parlement flamand.  Pour défendre une politique culturelle néerlandophone ambitieuse à Bruxelles et contre l'extrême droite. En effet, elle accède au pouvoir en Flandre, elle supprimera immédiatement le caractère critique et inclusif de notre ambitieuse politique culturelle." @Vooruit</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>663</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ik ben George ik ben cultuur mens een hart en heren toen ik eigenlijk als studenten uit het Leuvense aan de vb kwam studeren en 68 Dat was de grootste voor mij eh een hele uitdaging om eigenlijk te exploderen en ik heb dat vooral gedaan via cultuurorganisaties en die hebben mij eigenlijk Brussel bruisen Brussel leren kennen en dan heb ik eigenlijk ondervonden Hoe eigenlijk cultuurbeleid de creativiteit die in een stad heeft kan ondersteunen Daarom zei ik ook als cultuur ambtenaar van de Vlaamse gemeenschap dat ze morgen in Vlaanderen en een extreem rechtse regering aan de macht komt dan gaat men heel snel hakken en eigenlijk die Vlaamse subsidies in Brussel die essentieel zijn voor een heel creatief open inspirerend beleid dat de Vlaamse instellingen hier in Brussel kunnen voeren Het is voorraad of het is achteruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7.353302217224457e+18</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7353302217224457505</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1712074094</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024-04-02 09:08:14</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Een week geleden interpelleerde ik onderwijsminister Ben Weyts voor de zoveelste keer over het nijpende lerarentekort in onze stad.  Brussel schreeuwt om leerkrachten, maar de minister blijft Oost-Indisch doof. Noodmaatregelen zijn nu nodig. Want sterk onderwijs begint met sterke leerkrachten. 📺 Beelden: @BRUZZ en #vlaamsparlement</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2582</v>
+      </c>
+      <c r="I28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>We hebben nu nood aan extra noodmaatregelen specifiek voor Brussel Het is echt pompen op verzuipen vandaag in onze Brusselse scholen en u blijft dat eigenlijk op een of andere manier toch negeren Vlaams parlement lid voor vooruit Hannelore Goeman is niet mals voor onderwijs minister wijd die doet volgens haar te weinig om het gigantische leraren te kort in Brussel aan te pakken maar is dat nu zoveel teveel gevraagd om een aantal noodmaatregelen te nemen om ervoor te zorgen dat de scholen die compleet verzuipen onze kinderen naar school kunnen gaan dat hij nog meer ouders een telefoontje krijgen in het midden van het schooljaar dat dat een kind niet meer naar school kan omdat de klas toe gaat kan u zich die stress eigenlijk voorstellen of kan het uh eigenlijk niet genoeg schelen want ja het is maar Brussel we weten al langer dat de Vlaamse regering dat niet genoeg van wakker ligt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7.352087470718193e+18</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7352087470718192928</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1711791268</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024-03-30 02:34:28</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Leuk projectje in petto met mijn fantastische mede-kandidaten voor het Vlaams Parlement in Brussel. Stay tuned! 📽️ ••• Un petit projet amusant en vue avec mes fantastiques collègues candidats au Parlement flamand à Bruxelles. Restez à l’écoute ! 📽️ @Vooruit</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>703</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NO_SPEECH_DETECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7.351835604071599e+18</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7351835604071599392</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1711732621</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024-03-29 10:17:01</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hoe vaak &amp; hoe ver is Minister Weyts zijn boekje te buiten gegaan? Ben’s wil is wet? Het is simpel: inspectie moet in alle onafhankelijkheid kwaliteit van onderwijs controleren, daar heeft politiek zich niet mee te moeien. @Vooruit vraagt hoorzitting met Viaene, nu in reces.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>29100</v>
+      </c>
+      <c r="I30" t="n">
+        <v>380</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Wat een arrogantie de houding van minister weyts ten opzichte van de onderwijsinspectie is compleet onaanvaardbaar moeten wij nu echt normaal vinden dat de hoogste persoonlijke mening van de minister bepaalt wat er is op tijd te zijn van een individuele scholen doorlichting of dat het direct ingrijpt en zodat de Indiaan staan of the de kritisch zijn voor zijn gevaarlijke beleid of dat hij misschien zelfs rapporten achterhaalt mijn risico voor de gezondheid en de veiligheid van ons kinderen hoe dat ben wijzig op zelfs ten opzichte van de inspectie is gewoon schan dadelijk de onderwijsinspectie moet ik alle onafhankelijkheid zijn werk kunnen doen maar dat vindt ben wijs blijkbaar niet nodig dan zijn wil is wet iemand is gewoon een gevaar voor onze onderwijskwaliteit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7.351093402408127e+18</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hannelore.goeman/video/7351093402408127777</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1711559827</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024-03-27 10:17:07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Het lerarentekort in Brussel neemt dramatische proporties aan. Onze schoolteams verzuipen. Klassen gaan toe. Er wordt gespeeld met de toekomst van onze kinderen. En de minister van onderwijs? Die ligt er niet wakker van 🤯 Samen zijn onze Brusselse onderwijsschepenen Anaïs Maes, Bieke Comer, Saliha Raiss en Lydia Desloover trek ik daarom nog maar eens aan de alarmbel, met een open brief en een oproep aan Ben Weyts: we hebben noodmaatregelen nodig om onze Brusselse scholen recht te houden. Nu. Onmiddellijk.  📩  Lees onze open brief op www.knack.be @Vooruit</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>hannelore.goeman</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2185</v>
+      </c>
+      <c r="I31" t="n">
+        <v>37</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>vandaag voeren hier 20 Brussels die schone actie aan het kabinet rijdt van het leraar het wordt in Brussel neemt echt dramatische proporties aan onze schoolteams verzuipen onze kinderen krijg je geen les Als Brusselse onderwijs geven naar roeien we met riemen die we hebben maar het gigantische probleem van het leraren tekort kunnen we niet alleen rechttrekken wij nemen onze verantwoordelijkheid En we verwachten van de minister hetzelfde leerkrachten willen vandaag extra ondersteuning in de klas vinden we echt geen leerkrachten laat ons dan extra onder en aannemer dat doen we dan vandaag al maar alleen met ons gemeentelijke budget zorg dat leerkrachten niet zomaar in het midden van de schooljaar kunnen vertrekken want dat zet onze school teams extra onderdruk en vervang ik zoeken is heel moeilijk maar boven al meneer de minister zet je rond tafel met alle Brusselse onderwijs Partners We hebben dringend een actieplan nodig Het is niet vijf voor maar vijf na 12 schiet in actie minister weyts want onze Brusselse kinderen hebben recht op het sterk onderwijs sterk onderwijs sterke leerkrachten</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>katiasegers</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7317229350372396321</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B32" t="n">
+        <v>7.317229350372396e+18</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@katiasegers/video/7317229350372396321</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D32" t="n">
         <v>1703675237</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>2023-12-27 03:07:17</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>katiasegers</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H32" t="n">
         <v>1211</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I32" t="n">
         <v>27</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ik wil deze nacht in de straten mevrouw de klei van de stappen en zeer lang plezier överallt niet veel van een vrouw in het Nederlands landen van samen de wereld versterker met blinkende klas de Wolf aan Ze waren we met de mensen dat hebben we later zijn achternaam de Ik wil deze nacht in de straten mevrouw en de klein van de stad maakt mijn zeer langs dan heb je geen geld om plezier te vouwen en kreeg van vrouwen Naar De Kust</t>
+        </is>
       </c>
     </row>
   </sheetData>
